--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/FLORIDA_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/FLORIDA_2015.xlsx
@@ -553,7 +553,7 @@
         <v>3</v>
       </c>
       <c r="D11">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="12">
@@ -823,7 +823,7 @@
         <v>3</v>
       </c>
       <c r="D26">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="27">
@@ -949,7 +949,7 @@
         <v>3</v>
       </c>
       <c r="D33">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="34">
@@ -967,7 +967,7 @@
         <v>3</v>
       </c>
       <c r="D34">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="35">
@@ -1237,7 +1237,7 @@
         <v>3</v>
       </c>
       <c r="D49">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="50">
@@ -2389,7 +2389,7 @@
         <v>30</v>
       </c>
       <c r="D113">
-        <v>0.0009242998428690267</v>
+        <v>0.0009242998428690268</v>
       </c>
     </row>
     <row r="114">
@@ -2443,7 +2443,7 @@
         <v>3</v>
       </c>
       <c r="D116">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="117">
@@ -2533,7 +2533,7 @@
         <v>30</v>
       </c>
       <c r="D121">
-        <v>0.0009242998428690267</v>
+        <v>0.0009242998428690268</v>
       </c>
     </row>
     <row r="122">
@@ -2677,7 +2677,7 @@
         <v>3</v>
       </c>
       <c r="D129">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="130">
@@ -3199,7 +3199,7 @@
         <v>3</v>
       </c>
       <c r="D158">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="159">
@@ -3415,7 +3415,7 @@
         <v>3</v>
       </c>
       <c r="D170">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="171">
@@ -3595,7 +3595,7 @@
         <v>3</v>
       </c>
       <c r="D180">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="181">
@@ -3685,7 +3685,7 @@
         <v>3</v>
       </c>
       <c r="D185">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="186">
@@ -3775,7 +3775,7 @@
         <v>3</v>
       </c>
       <c r="D190">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="191">
@@ -3829,7 +3829,7 @@
         <v>3</v>
       </c>
       <c r="D193">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="194">
@@ -4441,7 +4441,7 @@
         <v>3</v>
       </c>
       <c r="D227">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="228">
@@ -4459,7 +4459,7 @@
         <v>3</v>
       </c>
       <c r="D228">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="229">
@@ -4603,7 +4603,7 @@
         <v>3</v>
       </c>
       <c r="D236">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="237">
@@ -5359,7 +5359,7 @@
         <v>3</v>
       </c>
       <c r="D278">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="279">
@@ -5647,7 +5647,7 @@
         <v>3</v>
       </c>
       <c r="D294">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="295">
@@ -5899,7 +5899,7 @@
         <v>3</v>
       </c>
       <c r="D308">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="309">
@@ -6169,7 +6169,7 @@
         <v>3</v>
       </c>
       <c r="D323">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="324">
@@ -6187,7 +6187,7 @@
         <v>3</v>
       </c>
       <c r="D324">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="325">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C362">
@@ -8077,7 +8077,7 @@
         <v>30</v>
       </c>
       <c r="D429">
-        <v>0.0009242998428690267</v>
+        <v>0.0009242998428690268</v>
       </c>
     </row>
     <row r="430">
@@ -8329,7 +8329,7 @@
         <v>30</v>
       </c>
       <c r="D443">
-        <v>0.0009242998428690267</v>
+        <v>0.0009242998428690268</v>
       </c>
     </row>
     <row r="444">
@@ -8347,7 +8347,7 @@
         <v>3</v>
       </c>
       <c r="D444">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="445">
@@ -8743,7 +8743,7 @@
         <v>3</v>
       </c>
       <c r="D466">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="467">
@@ -8851,7 +8851,7 @@
         <v>3</v>
       </c>
       <c r="D472">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="473">
@@ -8977,7 +8977,7 @@
         <v>3</v>
       </c>
       <c r="D479">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="480">
@@ -9193,7 +9193,7 @@
         <v>3</v>
       </c>
       <c r="D491">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="492">
@@ -9535,7 +9535,7 @@
         <v>3</v>
       </c>
       <c r="D510">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="511">
@@ -9679,7 +9679,7 @@
         <v>3</v>
       </c>
       <c r="D518">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="519">
@@ -9733,7 +9733,7 @@
         <v>3</v>
       </c>
       <c r="D521">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="522">
@@ -9751,7 +9751,7 @@
         <v>30</v>
       </c>
       <c r="D522">
-        <v>0.0009242998428690267</v>
+        <v>0.0009242998428690268</v>
       </c>
     </row>
     <row r="523">
@@ -9877,7 +9877,7 @@
         <v>3</v>
       </c>
       <c r="D529">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="530">
@@ -10579,7 +10579,7 @@
         <v>3</v>
       </c>
       <c r="D568">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="569">
@@ -10885,7 +10885,7 @@
         <v>3</v>
       </c>
       <c r="D585">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="586">
@@ -11047,7 +11047,7 @@
         <v>3</v>
       </c>
       <c r="D594">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="595">
@@ -11209,7 +11209,7 @@
         <v>3</v>
       </c>
       <c r="D603">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="604">
@@ -11515,7 +11515,7 @@
         <v>3</v>
       </c>
       <c r="D620">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="621">
@@ -11569,7 +11569,7 @@
         <v>3</v>
       </c>
       <c r="D623">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="624">
@@ -11659,7 +11659,7 @@
         <v>3</v>
       </c>
       <c r="D628">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="629">
@@ -12073,7 +12073,7 @@
         <v>3</v>
       </c>
       <c r="D651">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="652">
@@ -12667,7 +12667,7 @@
         <v>3</v>
       </c>
       <c r="D684">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="685">
@@ -12721,7 +12721,7 @@
         <v>30</v>
       </c>
       <c r="D687">
-        <v>0.0009242998428690267</v>
+        <v>0.0009242998428690268</v>
       </c>
     </row>
     <row r="688">
@@ -13261,7 +13261,7 @@
         <v>3</v>
       </c>
       <c r="D717">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="718">
@@ -13639,7 +13639,7 @@
         <v>3</v>
       </c>
       <c r="D738">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="739">
@@ -13729,7 +13729,7 @@
         <v>3</v>
       </c>
       <c r="D743">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="744">
@@ -13999,7 +13999,7 @@
         <v>3</v>
       </c>
       <c r="D758">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="759">
@@ -14143,7 +14143,7 @@
         <v>3</v>
       </c>
       <c r="D766">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="767">
@@ -14449,7 +14449,7 @@
         <v>3</v>
       </c>
       <c r="D783">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="784">
@@ -14521,7 +14521,7 @@
         <v>3</v>
       </c>
       <c r="D787">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="788">
@@ -14856,7 +14856,7 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C806">
@@ -14874,7 +14874,7 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>General Trevino</t>
+          <t>Gral. Trevino</t>
         </is>
       </c>
       <c r="C807">
@@ -15241,7 +15241,7 @@
         <v>3</v>
       </c>
       <c r="D827">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="828">
@@ -15439,7 +15439,7 @@
         <v>3</v>
       </c>
       <c r="D838">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="839">
@@ -15547,7 +15547,7 @@
         <v>30</v>
       </c>
       <c r="D844">
-        <v>0.0009242998428690267</v>
+        <v>0.0009242998428690268</v>
       </c>
     </row>
     <row r="845">
@@ -15709,7 +15709,7 @@
         <v>3</v>
       </c>
       <c r="D853">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="854">
@@ -15871,7 +15871,7 @@
         <v>3</v>
       </c>
       <c r="D862">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="863">
@@ -15925,7 +15925,7 @@
         <v>3</v>
       </c>
       <c r="D865">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="866">
@@ -16177,7 +16177,7 @@
         <v>3</v>
       </c>
       <c r="D879">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="880">
@@ -16339,7 +16339,7 @@
         <v>3</v>
       </c>
       <c r="D888">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="889">
@@ -16357,7 +16357,7 @@
         <v>3</v>
       </c>
       <c r="D889">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="890">
@@ -16627,7 +16627,7 @@
         <v>3</v>
       </c>
       <c r="D904">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="905">
@@ -16699,7 +16699,7 @@
         <v>3</v>
       </c>
       <c r="D908">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="909">
@@ -17023,7 +17023,7 @@
         <v>3</v>
       </c>
       <c r="D926">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="927">
@@ -17059,7 +17059,7 @@
         <v>3</v>
       </c>
       <c r="D928">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="929">
@@ -17437,7 +17437,7 @@
         <v>3</v>
       </c>
       <c r="D949">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="950">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C958">
@@ -17610,7 +17610,7 @@
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C959">
@@ -17689,7 +17689,7 @@
         <v>3</v>
       </c>
       <c r="D963">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="964">
@@ -17887,7 +17887,7 @@
         <v>3</v>
       </c>
       <c r="D974">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="975">
@@ -18373,7 +18373,7 @@
         <v>3</v>
       </c>
       <c r="D1001">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1002">
@@ -18427,7 +18427,7 @@
         <v>3</v>
       </c>
       <c r="D1004">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1005">
@@ -18571,7 +18571,7 @@
         <v>3</v>
       </c>
       <c r="D1012">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1013">
@@ -18715,7 +18715,7 @@
         <v>3</v>
       </c>
       <c r="D1020">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1021">
@@ -18733,7 +18733,7 @@
         <v>3</v>
       </c>
       <c r="D1021">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1022">
@@ -18895,7 +18895,7 @@
         <v>3</v>
       </c>
       <c r="D1030">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1031">
@@ -18924,7 +18924,7 @@
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1032">
@@ -19111,7 +19111,7 @@
         <v>3</v>
       </c>
       <c r="D1042">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1043">
@@ -19129,7 +19129,7 @@
         <v>3</v>
       </c>
       <c r="D1043">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1044">
@@ -19327,7 +19327,7 @@
         <v>3</v>
       </c>
       <c r="D1054">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1055">
@@ -19543,7 +19543,7 @@
         <v>3</v>
       </c>
       <c r="D1066">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1067">
@@ -19687,7 +19687,7 @@
         <v>3</v>
       </c>
       <c r="D1074">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1075">
@@ -19741,7 +19741,7 @@
         <v>3</v>
       </c>
       <c r="D1077">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1078">
@@ -20065,7 +20065,7 @@
         <v>3</v>
       </c>
       <c r="D1095">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1096">
@@ -20101,7 +20101,7 @@
         <v>3</v>
       </c>
       <c r="D1097">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1098">
@@ -20281,7 +20281,7 @@
         <v>3</v>
       </c>
       <c r="D1107">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1108">
@@ -20317,7 +20317,7 @@
         <v>3</v>
       </c>
       <c r="D1109">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1110">
@@ -20533,7 +20533,7 @@
         <v>3</v>
       </c>
       <c r="D1121">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1122">
@@ -20713,7 +20713,7 @@
         <v>3</v>
       </c>
       <c r="D1131">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1132">
@@ -21199,7 +21199,7 @@
         <v>3</v>
       </c>
       <c r="D1158">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1159">
@@ -21343,7 +21343,7 @@
         <v>3</v>
       </c>
       <c r="D1166">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1167">
@@ -21451,7 +21451,7 @@
         <v>3</v>
       </c>
       <c r="D1172">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1173">
@@ -21469,7 +21469,7 @@
         <v>3</v>
       </c>
       <c r="D1173">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1174">
@@ -21505,7 +21505,7 @@
         <v>3</v>
       </c>
       <c r="D1175">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1176">
@@ -21613,7 +21613,7 @@
         <v>3</v>
       </c>
       <c r="D1181">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1182">
@@ -21721,7 +21721,7 @@
         <v>3</v>
       </c>
       <c r="D1187">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1188">
@@ -21973,7 +21973,7 @@
         <v>3</v>
       </c>
       <c r="D1201">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1202">
@@ -22189,7 +22189,7 @@
         <v>3</v>
       </c>
       <c r="D1213">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1214">
@@ -22225,7 +22225,7 @@
         <v>3</v>
       </c>
       <c r="D1215">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1216">
@@ -22243,7 +22243,7 @@
         <v>3</v>
       </c>
       <c r="D1216">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1217">
@@ -22351,7 +22351,7 @@
         <v>3</v>
       </c>
       <c r="D1222">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1223">
@@ -22459,7 +22459,7 @@
         <v>3</v>
       </c>
       <c r="D1228">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1229">
@@ -22585,7 +22585,7 @@
         <v>3</v>
       </c>
       <c r="D1235">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1236">
@@ -23125,7 +23125,7 @@
         <v>3</v>
       </c>
       <c r="D1265">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1266">
@@ -23413,7 +23413,7 @@
         <v>3</v>
       </c>
       <c r="D1281">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1282">
@@ -23611,7 +23611,7 @@
         <v>3</v>
       </c>
       <c r="D1292">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1293">
@@ -24007,7 +24007,7 @@
         <v>3</v>
       </c>
       <c r="D1314">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1315">
@@ -24187,7 +24187,7 @@
         <v>3</v>
       </c>
       <c r="D1324">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1325">
@@ -24295,7 +24295,7 @@
         <v>3</v>
       </c>
       <c r="D1330">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1331">
@@ -25051,7 +25051,7 @@
         <v>30</v>
       </c>
       <c r="D1372">
-        <v>0.0009242998428690267</v>
+        <v>0.0009242998428690268</v>
       </c>
     </row>
     <row r="1373">
@@ -25267,7 +25267,7 @@
         <v>3</v>
       </c>
       <c r="D1384">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1385">
@@ -25375,7 +25375,7 @@
         <v>30</v>
       </c>
       <c r="D1390">
-        <v>0.0009242998428690267</v>
+        <v>0.0009242998428690268</v>
       </c>
     </row>
     <row r="1391">
@@ -25501,7 +25501,7 @@
         <v>30</v>
       </c>
       <c r="D1397">
-        <v>0.0009242998428690267</v>
+        <v>0.0009242998428690268</v>
       </c>
     </row>
     <row r="1398">
@@ -25627,7 +25627,7 @@
         <v>3</v>
       </c>
       <c r="D1404">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1405">
@@ -25699,7 +25699,7 @@
         <v>3</v>
       </c>
       <c r="D1408">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1409">
@@ -25951,7 +25951,7 @@
         <v>3</v>
       </c>
       <c r="D1422">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1423">
@@ -26131,7 +26131,7 @@
         <v>3</v>
       </c>
       <c r="D1432">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1433">
@@ -26833,7 +26833,7 @@
         <v>3</v>
       </c>
       <c r="D1471">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1472">
@@ -26887,7 +26887,7 @@
         <v>3</v>
       </c>
       <c r="D1474">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1475">
@@ -27031,7 +27031,7 @@
         <v>3</v>
       </c>
       <c r="D1482">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1483">
@@ -27229,7 +27229,7 @@
         <v>3</v>
       </c>
       <c r="D1493">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1494">
@@ -27409,7 +27409,7 @@
         <v>3</v>
       </c>
       <c r="D1503">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1504">
@@ -27697,7 +27697,7 @@
         <v>3</v>
       </c>
       <c r="D1519">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1520">
@@ -28255,7 +28255,7 @@
         <v>3</v>
       </c>
       <c r="D1550">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1551">
@@ -28273,7 +28273,7 @@
         <v>3</v>
       </c>
       <c r="D1551">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1552">
@@ -28561,7 +28561,7 @@
         <v>3</v>
       </c>
       <c r="D1567">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1568">
@@ -28597,7 +28597,7 @@
         <v>3</v>
       </c>
       <c r="D1569">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1570">
@@ -28723,7 +28723,7 @@
         <v>3</v>
       </c>
       <c r="D1576">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1577">
@@ -28975,7 +28975,7 @@
         <v>3</v>
       </c>
       <c r="D1590">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1591">
@@ -29047,7 +29047,7 @@
         <v>3</v>
       </c>
       <c r="D1594">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1595">
@@ -29641,7 +29641,7 @@
         <v>3</v>
       </c>
       <c r="D1627">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1628">
@@ -29713,7 +29713,7 @@
         <v>3</v>
       </c>
       <c r="D1631">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1632">
@@ -30217,7 +30217,7 @@
         <v>3</v>
       </c>
       <c r="D1659">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1660">
@@ -30451,7 +30451,7 @@
         <v>3</v>
       </c>
       <c r="D1672">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1673">
@@ -30595,7 +30595,7 @@
         <v>3</v>
       </c>
       <c r="D1680">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1681">
@@ -30631,7 +30631,7 @@
         <v>3</v>
       </c>
       <c r="D1682">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1683">
@@ -30667,7 +30667,7 @@
         <v>3</v>
       </c>
       <c r="D1684">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1685">
@@ -30793,7 +30793,7 @@
         <v>3</v>
       </c>
       <c r="D1691">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1692">
@@ -31171,7 +31171,7 @@
         <v>3</v>
       </c>
       <c r="D1712">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1713">
@@ -31459,7 +31459,7 @@
         <v>3</v>
       </c>
       <c r="D1728">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1729">
@@ -31657,7 +31657,7 @@
         <v>3</v>
       </c>
       <c r="D1739">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1740">
@@ -31945,7 +31945,7 @@
         <v>3</v>
       </c>
       <c r="D1755">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1756">
@@ -31999,7 +31999,7 @@
         <v>3</v>
       </c>
       <c r="D1758">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1759">
@@ -32089,7 +32089,7 @@
         <v>3</v>
       </c>
       <c r="D1763">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1764">
@@ -32107,7 +32107,7 @@
         <v>30</v>
       </c>
       <c r="D1764">
-        <v>0.0009242998428690267</v>
+        <v>0.0009242998428690268</v>
       </c>
     </row>
     <row r="1765">
@@ -32269,7 +32269,7 @@
         <v>3</v>
       </c>
       <c r="D1773">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1774">
@@ -32323,7 +32323,7 @@
         <v>3</v>
       </c>
       <c r="D1776">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1777">
@@ -32341,7 +32341,7 @@
         <v>3</v>
       </c>
       <c r="D1777">
-        <v>9.242998428690267E-05</v>
+        <v>9.242998428690268E-05</v>
       </c>
     </row>
     <row r="1778">
